--- a/Cardiologie/Excel/cardio_7.xlsx
+++ b/Cardiologie/Excel/cardio_7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7FC60FD-6C53-4525-A20E-377B7CC5BF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA8D113-3C0B-4B77-A38F-0C791A66E27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="355">
   <si>
     <t>L'artériopathie oblitérante des membres inférieurs est l’équivalent d’une crise d’angor au niveau des jambes.</t>
   </si>
@@ -563,6 +563,528 @@
   </si>
   <si>
     <t>image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La claudication intermittente du stade II se manifeste par une douleur crampoïde à l'effort rappelant l'angor </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'AOMI est définie comme une manifestation de la maladie athérothrombotique affectant les artères périphériques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'AOMI est au contraire associée à une augmentation du risque d'infarctus, d'AVC et de décès </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte précise que c'est la conséquence d'une maladie générale athéromateuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'AOMI représente au contraire 90 % des artériopathies </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le risque d'événement cardiovasculaire chez ces patients est 3 à 5 fois plus élevé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'hypertension (et non l'hypotension) est listée comme l'un des principaux facteurs de risque </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'athérosclérose est responsable de 70 % des cas d'AOMI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La prévalence est relativement similaire dans les deux sexes au-delà de 65 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'artérite diabétique est décrite comme une forme plus sévère avec des lésions plus distales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le risque est 3 fois plus élevé chez l'homme avant 65 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La prévalence est de plus de 7 % après 60 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le pronostic est grave car l'AOMI est souvent associée à des lésions coronaires ou carotidiennes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'AOMI est associée à une atteinte des coronaires dans environ 50 % des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est associée à des lésions carotidiennes ou vertébrales dans 5 à 10 % des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document mentionne une association à un anévrisme de l'aorte abdominale dans environ 10 % des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'artérite sénile est responsable d'environ 5 % des cas d'AOMI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La localisation prédominante au niveau de la fémorale profonde concerne l'artérite diabétique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le rétrécissement athéroscléreux entraîne une diminution du débit et le développement de collatérales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'artérite emboligène est liée à la migration de caillots, de fibrine ou de cholestérol </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le stade III correspond au stade d'ischémie de repos avec des douleurs caractéristiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le stade IIIb est au contraire défini par des pressions de perfusion ≤ 50 mm Hg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examen sémiologique systématique et l'anamnèse sont les bases du diagnostic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette classification concerne l'AOMI chronique ; l'ischémie aiguë utilise la règle des 5P </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La thromboaspiration est citée comme base du traitement de l'ischémie aiguë </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les emboles sont d'origine cardiaque dans 80 % des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les signes cliniques de l'ischémie aiguë suivent la règle des 5P (Pain, Pallor, Pulselessness, Paresthesia, Paralysis) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les signes neurologiques (sensibilité, mobilité) sont des témoins de la gravité et doivent être recherchés </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'angio-IRM est effectivement inadéquate pour les artères ayant fait l'objet d'un stenting </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'ischémie aiguë est une urgence car des dégâts irréversibles surviennent après 6 heures </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examen clinique permet de se faire une idée réaliste de l'état artériel dans plus de 80 % des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'aorto-artériographie classique est un examen invasif par ponction fémorale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'angio-IRM nécessite l'injection de Gadolinium (peu néphrotoxique) et non de produit iodé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le rétrécissement entraîne au contraire une diminution progressive du débit sanguin </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Au-delà d'un certain point, la suppléance collatérale devient insuffisante pour éviter l'hypoxie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les douleurs de repos caractérisent le stade III ; le stade II se manifeste par la claudication </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est une technique d'exploration de la microcirculation évaluant le retentissement tissulaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document distingue les bilans non-invasifs (angio-IRM/CT) de l'artériographie classique invasive </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les pressions de perfusion diminuent en cas d'AOMI alors que la pression artérielle augmente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le réentrainement physique supervisé est le traitement initial idéal de la claudication intermittente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tout patient souffrant d'AOMI doit être sous aspirine (ou clopidogrel) sauf contre-indication </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les statines sont utilisées chez tout patient pour leur effet stabilisant des plaques d’athérome </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le stade III est défini comme le stade d'ischémie de repos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les troubles trophiques sont localisés aux pieds et aux orteils </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'angio-CT ne permet pas une bonne visualisation des artères très calcifiées </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte précise que les emboles peuvent passer inaperçus (petites taches, orteil bleu) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les lésions peuvent être minimes (plaies interdigitales, crevasses) ou extensives </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La disparition des pouls est l'un des signes caractéristiques (Pulselessness) de l'ischémie aiguë </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'ischémie est responsable de lésions neurologiques dès la 4e heure </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont d'origine cardiaque dans 80 % des cas et artérielle dans 10 % des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'angio-IRM nécessite l'injection de Gadolinium, décrit comme un produit peu néphrotoxique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examen clinique permet au contraire de diagnostiquer l'état artériel dans plus de 80 % des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'angio-IRM et l'angio-CT sont citées comme des moyens non-invasifs de cartographie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'IRM utilise la résonance magnétique, contrairement au scanner qui utilise les rayons X et l'iode </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On constate une diminution des pressions de perfusion alors que la pression artérielle augmente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le réentrainement permet d'accroître significativement le périmètre de marche </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les lésions prédominent au niveau des artères jambières et des pieds </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle donne une cartographie de la vascularisation (artères), pas de la microcirculation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'angio-CT est une technique par tomodensitométrie avec injection de produit de contraste iodé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les lésions neurologiques surviennent dès la 4e heure </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'angio-CT est cité comme un bilan de cartographie non-invasif (par opposition à l'artériographie classique) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les pressions de perfusion (PP) au Doppler augmentent normalement en même temps que la PA à l'effort </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document ne mentionne pas le temps de recoloration unguéale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document ne mentionne pas de recommandation spécifique sur l'utilisation de la pulpe des doigts </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document ne mentionne pas la localisation anatomique de la bifurcation de l'aorte </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le pouls de l'artère pédieuse est effectivement mesuré, mais sa prise au 2ème métatarsien n'est pas précisée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'insuffisance veineuse est citée (signe associé de claudication), mais l'oedème à godet n'est pas spécifié </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document mentionne la présence de souffles artériels sans corrélation avec l'intensité </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La peau est décrite comme mal oxygénée (hypoxémie tissulaire), fine et fragile, mais sans précision sur la couleur rouge </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document ne mentionne pas spécifiquement le follicule pileux comme première structure à souffrir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les patients diabétiques présentent effectivement une atteinte neurologique (polyneuropathie) réduisant la sensation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'érythrocyanose n'est pas mentionnée ; le document parle de livedo ou de taches purpuriques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le test d'Allen n'est pas mentionné dans ce chapitre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La douleur de repos (stade III) cède au contraire en position assise ou debout par augmentation de la pression hydrostatique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La médiacalcose (infiltration calcaire) est fréquente en cas de diabète ou d'insuffisance rénale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'AOMI représente effectivement 90 % des artériopathies </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le risque d'événement coronarien ou cérébro-vasculaire est 3 à 5 fois plus élevé (pas 6x) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La prévalence de l’AOMI symptomatique est effectivement de 1 % avant 50 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les symptômes sont au contraire d'autant plus sévères qu'il y a une hypoxie tissulaire importante </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'athérosclérose est effectivement responsable de 70 % des AOMI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'AOMI par athérosclérose est décrite comme souvent localisée et d'évolution relativement lente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En cas de troubles trophiques liés à l'athérosclérose, ceux-ci sont souvent extensifs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document liste précisément l'aorte, les iliaques, les fémorales et les poplitées </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle touche préférentiellement les sujets âgés avec un rapport de 2 hommes pour 1 femme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'artérite diabétique est présente chez environ 20 % (soit 1/5) des artéritiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'artérite diabétique associe artérite athéromateuse et infiltration calcaire de la média </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'artérite diabétique touche effectivement des patients plus jeunes et évolue plus rapidement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle prédomine au niveau des artères jambières et de la fémorale profonde </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'artérite diabétique peut toucher n'importe quel gros tronc mais prédomine aux artères jambières </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'artérite sénile est liée à la fois à l'athérosclérose et à l'artériosclérose </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'artérite sénile est responsable d'environ 5 % des AOMI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est liée à la migration de caillots à partir de plaques de l'aorte, des iliaques ou fémorales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les emboles peuvent être d'origine artérielle ou cardiaque </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte précise explicitement que les emboles peuvent passer inaperçus </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document liste ces trois présentations cliniques pour l'artérite emboligène </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document ne mentionne pas la disparition des pouls périphériques spécifiquement pour l'étiologie emboligène </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le stade I est défini par une absence de symptômes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La claudication intermittente est effectivement le symptôme révélateur le plus fréquent </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le stade IIa est caractérisé par un périmètre de marche large (&gt; 200 m) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La claudication intermittente se définit par une douleur crampoïde obligeant à l'arrêt et cédant en 1-2 min </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La douleur intéresse différentes zones en fonction de la localisation des lésions artérielles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La claudication artérielle oblige effectivement à l'arrêt rapide et la récupération se fait en quelques minutes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La claudication d'origine artérielle apparaît effectivement "toujours la même" (distance de marche) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document mentionne l'impuissance comme signe associé neurologique, pas artériel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La douleur de stade III (repos) cède au contraire à la position assise ou debout </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'ischémie critique correspond au stade IIIb (et non IIIc qui n'existe pas dans le texte) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le patient est réveillé la nuit et finit par dormir au fauteuil pour augmenter la pression de perfusion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La gangrène (troubles trophiques) est caractéristique du stade IV (pas V) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tout traumatisme minime sur terrain d'artérite sévère peut déclencher une gangrène </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le mal perforant plantaire (faux stade IV) est lié à une polyneuropathie diabétique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'ABI (ou IPP) est calculé par le rapport pression cheville / pression humérale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La mesure de l'ABI complète systématiquement l'examen clinique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Doppler mesure les pressions aux artères pédieuses, tibiales postérieures et humérales (pas antérieures) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'indice normal (ABI) se situe entre 1,3 et 1,0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document mentionne un ABI normal jusqu'à 1,3 ; au-delà il est souvent lié à la médiacalcose </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’ABI est le rapport entre la pression systolique (pas diastolique) de la cheville et du bras </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’indice ABI chute effectivement en cas d’artérite (&lt; 0,9) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le test de Strandness décèle une AOMI qui ne devient symptomatique qu'à l'effort </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le test mesure les pressions de perfusion au Doppler au repos et en fin d'effort </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La pression systolique est au contraire plus élevée à la cheville (artère tibiale) qu'au bras </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'épreuve est stoppée quand la douleur apparaît ou après maximum 5 minutes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En cas d’AOMI, on constate effectivement une diminution des PP alors que la PA augmente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La remontée est au contraire d'autant plus lente que les lésions sont sévères </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme que cet examen permet le diagnostic d'anévrismes aortiques et poplités </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le duplex scan correspond à une échographie couplée à un examen Doppler (pas un scanner) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examen est effectivement chronophage mais peut parfois éviter l'artériographie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il est utile pour évaluer l'extension des lésions et assurer le suivi des pontages </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les valeurs normales de tc pO2 se situent entre 40 et 60 mmHg chez le sujet en décubitus (pas debout) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les valeurs deviennent effectivement pathologiques quand elles sont inférieures à 35 mmHg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette technique d’exploration de la microcirculation évalue le retentissement tissulaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est utile pour évaluer les AOMI sévères quand les PP sont d'interprétation difficile </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle dépend de la PaO2, du débit sanguin local et de la diffusion (l'âge n'est pas cité) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les valeurs deviennent pathologiques quand elles sont inférieures à 35 mmHg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est un excellent examen de première approche pour visualiser les artères </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'angio-IRM a au contraire tendance à surestimer la sévérité des sténoses </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'angio-scanner (ou angio-CT) ne permet pas une bonne visualisation des artères calcifiées </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'insuffisance rénale et l'allergie à l'iode sont des contre-indications à l'angio-CT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'angio-CT nécessite une injection IV (pas intra-artérielle fémorale) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C’est un examen invasif qui nécessite effectivement un cathétérisme par voie artérielle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’aorto-artériographie nécessite au contraire l’injection d’un produit de contraste iodé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les objectifs sont de prévenir la morbidité/mortalité et d'essayer d'améliorer le confort </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il peut être proposé pour les stades III et IV, mais aussi parfois pour le stade IIb </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La modification des facteurs de risque permet de diminuer la morbidité et mortalité globale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le réentraînement physique supervisé est le traitement initial idéal de la claudication </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il permet d’accroître le périmètre de marche au point de parfois éviter d'autres traitements </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le programme doit comporter au moins 3 sessions (pas 5) de 30 minutes par semaine </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On utilise au contraire de petites doses d'aspirine (75 à 160 mg/j) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte souligne que le caractère contraignant explique le désintérêt rapide des patients </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte précise qu'elles ont peu d’utilité en termes d’accroissement du périmètre de marche </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles peuvent être utilisées en cas d'AOMI sévère sans possibilité d'intervention </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les prostaglandines citées (Pg I2 et Pg E1) ont un effet vasodilatateur puissant (pas vasoconstricteur) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement est proposé pour les stades III, IV ou claudication invalidante (stade IIb) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les meilleures indications sont l'aorte abdominale et les axes iliaques (pas les fémorales) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement endovasculaire permet de dilater les sténoses, pas d'éliminer l'athérome </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On utilise du PTFE pour les pontages sous-inguinaux (le Dacron est pour le carrefour aortique) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le matériel utilisé est effectivement soit une veine autologue, soit du matériel prothétique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le matériel prothétique est plus sensible aux infections et moins perméable à long terme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document liste effectivement ces quatre complications post-opératoires principales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est réalisée pour accroître la vasodilatation périphérique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle résulte en une peau sèche et chaude (pas humide) au niveau des pieds </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle peut se faire par voie chirurgicale ou par voie percutanée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'ischémie aiguë met effectivement en danger la viabilité et la fonction du membre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les lésions musculaires apparaissent dès la 6e heure </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La phlébite bleue est citée comme un autre mécanisme possible de l'ischémie aiguë </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La règle des 5P caractérise au contraire l'ischémie aiguë </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La dissection aortique étendue aux artères iliaques est une étiologie d'ischémie aiguë </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La thrombose est au contraire liée à un bas-débit systémique (choc) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les emboles sont effectivement d'origine cardiaque dans 80 % des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les paresthésies sont dues à l'ischémie des vasa nervorum </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La diminution de la sensibilité et de la mobilité témoigne de la gravité de l'ischémie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est une urgence car des dégâts irréversibles surviennent au-delà de 6 heures (pas 8h) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La sonde de Fogarty permet effectivement l'exérèse chirurgicale des emboles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement se base sur la thromboaspiration, les anticoagulants et l'exérèse chirurgicale </t>
+  </si>
+  <si>
+    <t>Page</t>
   </si>
 </sst>
 </file>
@@ -910,16 +1432,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G175"/>
+  <dimension ref="A1:H175"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="189.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="8.28515625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>174</v>
       </c>
@@ -933,16 +1456,19 @@
         <v>177</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -952,8 +1478,14 @@
       <c r="C2" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E2" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -963,8 +1495,14 @@
       <c r="C3" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -974,8 +1512,14 @@
       <c r="C4" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -985,8 +1529,14 @@
       <c r="C5" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -996,8 +1546,14 @@
       <c r="C6" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>185</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1007,8 +1563,14 @@
       <c r="C7" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>186</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1018,8 +1580,14 @@
       <c r="C8" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>187</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1029,8 +1597,14 @@
       <c r="C9" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>188</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1040,8 +1614,14 @@
       <c r="C10" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>189</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1051,8 +1631,14 @@
       <c r="C11" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1062,8 +1648,14 @@
       <c r="C12" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>191</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1073,8 +1665,14 @@
       <c r="C13" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>192</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1084,8 +1682,14 @@
       <c r="C14" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1095,8 +1699,14 @@
       <c r="C15" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>194</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1106,8 +1716,14 @@
       <c r="C16" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>195</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1117,8 +1733,14 @@
       <c r="C17" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>196</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1128,8 +1750,14 @@
       <c r="C18" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>197</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1139,8 +1767,14 @@
       <c r="C19" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>198</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1150,8 +1784,14 @@
       <c r="C20" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>199</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1161,8 +1801,14 @@
       <c r="C21" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>200</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1172,8 +1818,14 @@
       <c r="C22" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>201</v>
+      </c>
+      <c r="E22" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1183,8 +1835,14 @@
       <c r="C23" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>202</v>
+      </c>
+      <c r="E23" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1194,8 +1852,14 @@
       <c r="C24" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>203</v>
+      </c>
+      <c r="E24" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1205,8 +1869,14 @@
       <c r="C25" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>204</v>
+      </c>
+      <c r="E25" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1216,8 +1886,14 @@
       <c r="C26" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>205</v>
+      </c>
+      <c r="E26" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1227,8 +1903,14 @@
       <c r="C27" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>206</v>
+      </c>
+      <c r="E27" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1238,8 +1920,14 @@
       <c r="C28" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>207</v>
+      </c>
+      <c r="E28" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1249,8 +1937,14 @@
       <c r="C29" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>208</v>
+      </c>
+      <c r="E29" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1260,8 +1954,14 @@
       <c r="C30" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E30" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1271,8 +1971,14 @@
       <c r="C31" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>210</v>
+      </c>
+      <c r="E31" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1282,8 +1988,14 @@
       <c r="C32" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>211</v>
+      </c>
+      <c r="E32" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1293,8 +2005,14 @@
       <c r="C33" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>212</v>
+      </c>
+      <c r="E33" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1304,8 +2022,14 @@
       <c r="C34" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>213</v>
+      </c>
+      <c r="E34" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1315,8 +2039,14 @@
       <c r="C35" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>214</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1326,8 +2056,14 @@
       <c r="C36" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>215</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1337,8 +2073,14 @@
       <c r="C37" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>216</v>
+      </c>
+      <c r="E37" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1348,8 +2090,14 @@
       <c r="C38" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>217</v>
+      </c>
+      <c r="E38" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1359,8 +2107,14 @@
       <c r="C39" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>218</v>
+      </c>
+      <c r="E39" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1370,8 +2124,14 @@
       <c r="C40" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>219</v>
+      </c>
+      <c r="E40" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1381,8 +2141,14 @@
       <c r="C41" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
+        <v>220</v>
+      </c>
+      <c r="E41" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -1392,8 +2158,14 @@
       <c r="C42" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>221</v>
+      </c>
+      <c r="E42" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -1403,8 +2175,14 @@
       <c r="C43" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>222</v>
+      </c>
+      <c r="E43" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -1414,8 +2192,14 @@
       <c r="C44" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>223</v>
+      </c>
+      <c r="E44" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -1425,8 +2209,14 @@
       <c r="C45" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>224</v>
+      </c>
+      <c r="E45" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -1436,8 +2226,14 @@
       <c r="C46" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>225</v>
+      </c>
+      <c r="E46" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -1447,8 +2243,14 @@
       <c r="C47" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>226</v>
+      </c>
+      <c r="E47" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -1458,8 +2260,14 @@
       <c r="C48" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
+        <v>227</v>
+      </c>
+      <c r="E48" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -1469,8 +2277,14 @@
       <c r="C49" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
+        <v>228</v>
+      </c>
+      <c r="E49" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -1480,8 +2294,14 @@
       <c r="C50" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50" t="s">
+        <v>229</v>
+      </c>
+      <c r="E50" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -1491,8 +2311,14 @@
       <c r="C51" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D51" t="s">
+        <v>230</v>
+      </c>
+      <c r="E51" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -1502,8 +2328,14 @@
       <c r="C52" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D52" t="s">
+        <v>231</v>
+      </c>
+      <c r="E52" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -1513,8 +2345,14 @@
       <c r="C53" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53" t="s">
+        <v>232</v>
+      </c>
+      <c r="E53" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -1524,8 +2362,14 @@
       <c r="C54" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D54" t="s">
+        <v>233</v>
+      </c>
+      <c r="E54" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -1535,8 +2379,14 @@
       <c r="C55" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55" t="s">
+        <v>234</v>
+      </c>
+      <c r="E55" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -1546,8 +2396,14 @@
       <c r="C56" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56" t="s">
+        <v>235</v>
+      </c>
+      <c r="E56" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -1557,8 +2413,14 @@
       <c r="C57" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D57" t="s">
+        <v>236</v>
+      </c>
+      <c r="E57" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -1568,8 +2430,14 @@
       <c r="C58" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D58" t="s">
+        <v>237</v>
+      </c>
+      <c r="E58" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -1579,8 +2447,14 @@
       <c r="C59" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D59" t="s">
+        <v>238</v>
+      </c>
+      <c r="E59" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -1590,8 +2464,14 @@
       <c r="C60" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60" t="s">
+        <v>239</v>
+      </c>
+      <c r="E60" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -1601,8 +2481,14 @@
       <c r="C61" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D61" t="s">
+        <v>240</v>
+      </c>
+      <c r="E61" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -1612,8 +2498,14 @@
       <c r="C62" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D62" t="s">
+        <v>241</v>
+      </c>
+      <c r="E62" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -1623,8 +2515,14 @@
       <c r="C63" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63" t="s">
+        <v>242</v>
+      </c>
+      <c r="E63" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -1634,8 +2532,14 @@
       <c r="C64" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D64" t="s">
+        <v>243</v>
+      </c>
+      <c r="E64" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -1645,8 +2549,14 @@
       <c r="C65" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D65" t="s">
+        <v>244</v>
+      </c>
+      <c r="E65" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -1656,8 +2566,14 @@
       <c r="C66" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D66" t="s">
+        <v>245</v>
+      </c>
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -1667,8 +2583,14 @@
       <c r="C67" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D67" t="s">
+        <v>246</v>
+      </c>
+      <c r="E67" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -1678,8 +2600,14 @@
       <c r="C68" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D68" t="s">
+        <v>247</v>
+      </c>
+      <c r="E68" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -1689,8 +2617,14 @@
       <c r="C69" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D69" t="s">
+        <v>248</v>
+      </c>
+      <c r="E69" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -1700,8 +2634,14 @@
       <c r="C70" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D70" t="s">
+        <v>249</v>
+      </c>
+      <c r="E70" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -1711,8 +2651,14 @@
       <c r="C71" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D71" t="s">
+        <v>250</v>
+      </c>
+      <c r="E71" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -1722,8 +2668,14 @@
       <c r="C72" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D72" t="s">
+        <v>251</v>
+      </c>
+      <c r="E72" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -1733,8 +2685,14 @@
       <c r="C73" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D73" t="s">
+        <v>252</v>
+      </c>
+      <c r="E73" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -1744,8 +2702,14 @@
       <c r="C74" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D74" t="s">
+        <v>253</v>
+      </c>
+      <c r="E74" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -1755,8 +2719,14 @@
       <c r="C75" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D75" t="s">
+        <v>254</v>
+      </c>
+      <c r="E75" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -1766,8 +2736,14 @@
       <c r="C76" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D76" t="s">
+        <v>255</v>
+      </c>
+      <c r="E76" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -1777,8 +2753,14 @@
       <c r="C77" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D77" t="s">
+        <v>256</v>
+      </c>
+      <c r="E77" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -1788,8 +2770,14 @@
       <c r="C78" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D78" t="s">
+        <v>257</v>
+      </c>
+      <c r="E78" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -1799,8 +2787,14 @@
       <c r="C79" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D79" t="s">
+        <v>258</v>
+      </c>
+      <c r="E79" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -1810,8 +2804,14 @@
       <c r="C80" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D80" t="s">
+        <v>259</v>
+      </c>
+      <c r="E80" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -1821,8 +2821,14 @@
       <c r="C81" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D81" t="s">
+        <v>260</v>
+      </c>
+      <c r="E81" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -1832,8 +2838,14 @@
       <c r="C82" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D82" t="s">
+        <v>261</v>
+      </c>
+      <c r="E82" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -1843,8 +2855,14 @@
       <c r="C83" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D83" t="s">
+        <v>262</v>
+      </c>
+      <c r="E83" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -1854,8 +2872,14 @@
       <c r="C84" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D84" t="s">
+        <v>263</v>
+      </c>
+      <c r="E84" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -1865,8 +2889,14 @@
       <c r="C85" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D85" t="s">
+        <v>264</v>
+      </c>
+      <c r="E85" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -1876,8 +2906,14 @@
       <c r="C86" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D86" t="s">
+        <v>265</v>
+      </c>
+      <c r="E86" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -1887,8 +2923,14 @@
       <c r="C87" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D87" t="s">
+        <v>190</v>
+      </c>
+      <c r="E87" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -1898,8 +2940,14 @@
       <c r="C88" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D88" t="s">
+        <v>266</v>
+      </c>
+      <c r="E88" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -1909,8 +2957,14 @@
       <c r="C89" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D89" t="s">
+        <v>267</v>
+      </c>
+      <c r="E89" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -1920,8 +2974,14 @@
       <c r="C90" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D90" t="s">
+        <v>268</v>
+      </c>
+      <c r="E90" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -1931,8 +2991,14 @@
       <c r="C91" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D91" t="s">
+        <v>269</v>
+      </c>
+      <c r="E91" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -1942,8 +3008,14 @@
       <c r="C92" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D92" t="s">
+        <v>270</v>
+      </c>
+      <c r="E92" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -1953,8 +3025,14 @@
       <c r="C93" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D93" t="s">
+        <v>271</v>
+      </c>
+      <c r="E93" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -1964,8 +3042,14 @@
       <c r="C94" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D94" t="s">
+        <v>272</v>
+      </c>
+      <c r="E94" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -1975,8 +3059,14 @@
       <c r="C95" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D95" t="s">
+        <v>273</v>
+      </c>
+      <c r="E95" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -1986,8 +3076,14 @@
       <c r="C96" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D96" t="s">
+        <v>274</v>
+      </c>
+      <c r="E96" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -1997,8 +3093,14 @@
       <c r="C97" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D97" t="s">
+        <v>275</v>
+      </c>
+      <c r="E97" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -2008,8 +3110,14 @@
       <c r="C98" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D98" t="s">
+        <v>276</v>
+      </c>
+      <c r="E98" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -2019,8 +3127,14 @@
       <c r="C99" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D99" t="s">
+        <v>277</v>
+      </c>
+      <c r="E99" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -2030,8 +3144,14 @@
       <c r="C100" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D100" t="s">
+        <v>278</v>
+      </c>
+      <c r="E100" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -2041,8 +3161,14 @@
       <c r="C101" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D101" t="s">
+        <v>279</v>
+      </c>
+      <c r="E101" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -2052,8 +3178,14 @@
       <c r="C102" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D102" t="s">
+        <v>280</v>
+      </c>
+      <c r="E102" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -2063,8 +3195,14 @@
       <c r="C103" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D103" t="s">
+        <v>281</v>
+      </c>
+      <c r="E103" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -2074,8 +3212,14 @@
       <c r="C104" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D104" t="s">
+        <v>282</v>
+      </c>
+      <c r="E104" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -2085,8 +3229,14 @@
       <c r="C105" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D105" t="s">
+        <v>283</v>
+      </c>
+      <c r="E105" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -2096,8 +3246,14 @@
       <c r="C106" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D106" t="s">
+        <v>284</v>
+      </c>
+      <c r="E106" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -2107,8 +3263,14 @@
       <c r="C107" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D107" t="s">
+        <v>285</v>
+      </c>
+      <c r="E107" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -2118,8 +3280,14 @@
       <c r="C108" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D108" t="s">
+        <v>286</v>
+      </c>
+      <c r="E108" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -2129,8 +3297,14 @@
       <c r="C109" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D109" t="s">
+        <v>287</v>
+      </c>
+      <c r="E109" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -2140,8 +3314,14 @@
       <c r="C110" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D110" t="s">
+        <v>288</v>
+      </c>
+      <c r="E110" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -2151,8 +3331,14 @@
       <c r="C111" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D111" t="s">
+        <v>289</v>
+      </c>
+      <c r="E111" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -2162,8 +3348,14 @@
       <c r="C112" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D112" t="s">
+        <v>290</v>
+      </c>
+      <c r="E112" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -2173,8 +3365,14 @@
       <c r="C113" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D113" t="s">
+        <v>291</v>
+      </c>
+      <c r="E113" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -2184,8 +3382,14 @@
       <c r="C114" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D114" t="s">
+        <v>292</v>
+      </c>
+      <c r="E114" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -2195,8 +3399,14 @@
       <c r="C115" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D115" t="s">
+        <v>293</v>
+      </c>
+      <c r="E115" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -2206,8 +3416,14 @@
       <c r="C116" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D116" t="s">
+        <v>294</v>
+      </c>
+      <c r="E116" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -2217,8 +3433,14 @@
       <c r="C117" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D117" t="s">
+        <v>295</v>
+      </c>
+      <c r="E117" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -2228,8 +3450,14 @@
       <c r="C118" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D118" t="s">
+        <v>296</v>
+      </c>
+      <c r="E118" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -2239,8 +3467,14 @@
       <c r="C119" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D119" t="s">
+        <v>297</v>
+      </c>
+      <c r="E119" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -2250,8 +3484,14 @@
       <c r="C120" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D120" t="s">
+        <v>298</v>
+      </c>
+      <c r="E120" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -2261,8 +3501,14 @@
       <c r="C121" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D121" t="s">
+        <v>299</v>
+      </c>
+      <c r="E121" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -2272,8 +3518,14 @@
       <c r="C122" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D122" t="s">
+        <v>300</v>
+      </c>
+      <c r="E122" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -2283,8 +3535,14 @@
       <c r="C123" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D123" t="s">
+        <v>301</v>
+      </c>
+      <c r="E123" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>123</v>
       </c>
@@ -2294,8 +3552,14 @@
       <c r="C124" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D124" t="s">
+        <v>302</v>
+      </c>
+      <c r="E124" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -2305,8 +3569,14 @@
       <c r="C125" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D125" t="s">
+        <v>303</v>
+      </c>
+      <c r="E125" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -2316,8 +3586,14 @@
       <c r="C126" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D126" t="s">
+        <v>304</v>
+      </c>
+      <c r="E126" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>126</v>
       </c>
@@ -2327,8 +3603,14 @@
       <c r="C127" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D127" t="s">
+        <v>305</v>
+      </c>
+      <c r="E127" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -2338,8 +3620,14 @@
       <c r="C128" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D128" t="s">
+        <v>306</v>
+      </c>
+      <c r="E128" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>128</v>
       </c>
@@ -2349,8 +3637,14 @@
       <c r="C129" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D129" t="s">
+        <v>307</v>
+      </c>
+      <c r="E129" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>129</v>
       </c>
@@ -2360,8 +3654,14 @@
       <c r="C130" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D130" t="s">
+        <v>308</v>
+      </c>
+      <c r="E130" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>130</v>
       </c>
@@ -2371,8 +3671,14 @@
       <c r="C131" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D131" t="s">
+        <v>309</v>
+      </c>
+      <c r="E131" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>131</v>
       </c>
@@ -2382,8 +3688,14 @@
       <c r="C132" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D132" t="s">
+        <v>310</v>
+      </c>
+      <c r="E132" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -2393,8 +3705,14 @@
       <c r="C133" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D133" t="s">
+        <v>311</v>
+      </c>
+      <c r="E133" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -2404,8 +3722,14 @@
       <c r="C134" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D134" t="s">
+        <v>312</v>
+      </c>
+      <c r="E134" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -2415,8 +3739,14 @@
       <c r="C135" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D135" t="s">
+        <v>313</v>
+      </c>
+      <c r="E135" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -2426,8 +3756,14 @@
       <c r="C136" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D136" t="s">
+        <v>314</v>
+      </c>
+      <c r="E136" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>136</v>
       </c>
@@ -2437,8 +3773,14 @@
       <c r="C137" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D137" t="s">
+        <v>315</v>
+      </c>
+      <c r="E137" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -2448,8 +3790,14 @@
       <c r="C138" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D138" t="s">
+        <v>316</v>
+      </c>
+      <c r="E138" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -2459,8 +3807,14 @@
       <c r="C139" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D139" t="s">
+        <v>317</v>
+      </c>
+      <c r="E139" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -2470,8 +3824,14 @@
       <c r="C140" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D140" t="s">
+        <v>318</v>
+      </c>
+      <c r="E140" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>140</v>
       </c>
@@ -2481,8 +3841,14 @@
       <c r="C141" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D141" t="s">
+        <v>319</v>
+      </c>
+      <c r="E141" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>141</v>
       </c>
@@ -2492,8 +3858,14 @@
       <c r="C142" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D142" t="s">
+        <v>320</v>
+      </c>
+      <c r="E142" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -2503,8 +3875,14 @@
       <c r="C143" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D143" t="s">
+        <v>321</v>
+      </c>
+      <c r="E143" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>143</v>
       </c>
@@ -2514,8 +3892,14 @@
       <c r="C144" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D144" t="s">
+        <v>322</v>
+      </c>
+      <c r="E144" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>144</v>
       </c>
@@ -2525,8 +3909,14 @@
       <c r="C145" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D145" t="s">
+        <v>323</v>
+      </c>
+      <c r="E145" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>145</v>
       </c>
@@ -2536,8 +3926,14 @@
       <c r="C146" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D146" t="s">
+        <v>324</v>
+      </c>
+      <c r="E146" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>146</v>
       </c>
@@ -2547,8 +3943,14 @@
       <c r="C147" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D147" t="s">
+        <v>325</v>
+      </c>
+      <c r="E147" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>147</v>
       </c>
@@ -2558,8 +3960,14 @@
       <c r="C148" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D148" t="s">
+        <v>326</v>
+      </c>
+      <c r="E148" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>148</v>
       </c>
@@ -2569,8 +3977,14 @@
       <c r="C149" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D149" t="s">
+        <v>327</v>
+      </c>
+      <c r="E149" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>149</v>
       </c>
@@ -2580,8 +3994,14 @@
       <c r="C150" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D150" t="s">
+        <v>328</v>
+      </c>
+      <c r="E150" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>150</v>
       </c>
@@ -2591,8 +4011,14 @@
       <c r="C151" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D151" t="s">
+        <v>329</v>
+      </c>
+      <c r="E151" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>151</v>
       </c>
@@ -2602,8 +4028,14 @@
       <c r="C152" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D152" t="s">
+        <v>330</v>
+      </c>
+      <c r="E152" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>152</v>
       </c>
@@ -2613,8 +4045,14 @@
       <c r="C153" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D153" t="s">
+        <v>331</v>
+      </c>
+      <c r="E153" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>153</v>
       </c>
@@ -2624,8 +4062,14 @@
       <c r="C154" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D154" t="s">
+        <v>332</v>
+      </c>
+      <c r="E154" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>154</v>
       </c>
@@ -2635,8 +4079,14 @@
       <c r="C155" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D155" t="s">
+        <v>333</v>
+      </c>
+      <c r="E155" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>155</v>
       </c>
@@ -2646,8 +4096,14 @@
       <c r="C156" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D156" t="s">
+        <v>334</v>
+      </c>
+      <c r="E156" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>156</v>
       </c>
@@ -2657,8 +4113,14 @@
       <c r="C157" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D157" t="s">
+        <v>335</v>
+      </c>
+      <c r="E157" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>157</v>
       </c>
@@ -2668,8 +4130,14 @@
       <c r="C158" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D158" t="s">
+        <v>336</v>
+      </c>
+      <c r="E158" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>158</v>
       </c>
@@ -2679,8 +4147,14 @@
       <c r="C159" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D159" t="s">
+        <v>337</v>
+      </c>
+      <c r="E159" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>159</v>
       </c>
@@ -2690,8 +4164,14 @@
       <c r="C160" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D160" t="s">
+        <v>338</v>
+      </c>
+      <c r="E160" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>160</v>
       </c>
@@ -2701,8 +4181,14 @@
       <c r="C161" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D161" t="s">
+        <v>339</v>
+      </c>
+      <c r="E161" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>161</v>
       </c>
@@ -2712,8 +4198,14 @@
       <c r="C162" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D162" t="s">
+        <v>340</v>
+      </c>
+      <c r="E162" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>162</v>
       </c>
@@ -2723,8 +4215,14 @@
       <c r="C163" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D163" t="s">
+        <v>341</v>
+      </c>
+      <c r="E163" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>163</v>
       </c>
@@ -2734,8 +4232,14 @@
       <c r="C164" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D164" t="s">
+        <v>342</v>
+      </c>
+      <c r="E164" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>164</v>
       </c>
@@ -2745,8 +4249,14 @@
       <c r="C165" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D165" t="s">
+        <v>343</v>
+      </c>
+      <c r="E165" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>165</v>
       </c>
@@ -2756,8 +4266,14 @@
       <c r="C166" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D166" t="s">
+        <v>344</v>
+      </c>
+      <c r="E166" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>166</v>
       </c>
@@ -2767,8 +4283,14 @@
       <c r="C167" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D167" t="s">
+        <v>345</v>
+      </c>
+      <c r="E167" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>167</v>
       </c>
@@ -2778,8 +4300,14 @@
       <c r="C168" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D168" t="s">
+        <v>346</v>
+      </c>
+      <c r="E168" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>168</v>
       </c>
@@ -2789,8 +4317,14 @@
       <c r="C169" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D169" t="s">
+        <v>347</v>
+      </c>
+      <c r="E169" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>169</v>
       </c>
@@ -2800,8 +4334,14 @@
       <c r="C170" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D170" t="s">
+        <v>348</v>
+      </c>
+      <c r="E170" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>170</v>
       </c>
@@ -2811,8 +4351,14 @@
       <c r="C171" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D171" t="s">
+        <v>349</v>
+      </c>
+      <c r="E171" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>171</v>
       </c>
@@ -2822,8 +4368,14 @@
       <c r="C172" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D172" t="s">
+        <v>350</v>
+      </c>
+      <c r="E172" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>172</v>
       </c>
@@ -2833,8 +4385,14 @@
       <c r="C173" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D173" t="s">
+        <v>351</v>
+      </c>
+      <c r="E173" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>173</v>
       </c>
@@ -2844,8 +4402,14 @@
       <c r="C174" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D174" t="s">
+        <v>352</v>
+      </c>
+      <c r="E174" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>174</v>
       </c>
@@ -2854,6 +4418,12 @@
       </c>
       <c r="C175" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="D175" t="s">
+        <v>353</v>
+      </c>
+      <c r="E175" s="1">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
